--- a/Result/profitability/5511.xlsx
+++ b/Result/profitability/5511.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AM74"/>
+  <dimension ref="A1:AM75"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -669,10 +669,10 @@
         <v>0.31</v>
       </c>
       <c r="M2" t="n">
-        <v>2.27625</v>
+        <v>2.32</v>
       </c>
       <c r="N2" t="n">
-        <v>15.83125</v>
+        <v>15.845</v>
       </c>
       <c r="O2" t="n">
         <v>0</v>
@@ -780,10 +780,10 @@
         <v>0.52</v>
       </c>
       <c r="M3" t="n">
-        <v>1.9575</v>
+        <v>2.1775</v>
       </c>
       <c r="N3" t="n">
-        <v>14.37</v>
+        <v>15.485</v>
       </c>
       <c r="O3" t="n">
         <v>0</v>
@@ -899,10 +899,10 @@
         <v>0.41</v>
       </c>
       <c r="M4" t="n">
-        <v>1.80125</v>
+        <v>2.085</v>
       </c>
       <c r="N4" t="n">
-        <v>13.78875</v>
+        <v>14.69125</v>
       </c>
       <c r="O4" t="n">
         <v>0</v>
@@ -1018,10 +1018,10 @@
         <v>0.26</v>
       </c>
       <c r="M5" t="n">
-        <v>1.69</v>
+        <v>1.88625</v>
       </c>
       <c r="N5" t="n">
-        <v>12.80125</v>
+        <v>13.3125</v>
       </c>
       <c r="O5" t="n">
         <v>0</v>
@@ -1137,10 +1137,10 @@
         <v>0.34</v>
       </c>
       <c r="M6" t="n">
-        <v>1.50125</v>
+        <v>1.485</v>
       </c>
       <c r="N6" t="n">
-        <v>11.4925</v>
+        <v>11.725</v>
       </c>
       <c r="O6" t="n">
         <v>0</v>
@@ -1264,10 +1264,10 @@
         <v>0.46</v>
       </c>
       <c r="M7" t="n">
-        <v>1.115</v>
+        <v>1.0325</v>
       </c>
       <c r="N7" t="n">
-        <v>10.0225</v>
+        <v>10.25375</v>
       </c>
       <c r="O7" t="n">
         <v>0</v>
@@ -1391,10 +1391,10 @@
         <v>0.38</v>
       </c>
       <c r="M8" t="n">
-        <v>0.6525</v>
+        <v>0.7625</v>
       </c>
       <c r="N8" t="n">
-        <v>8.49625</v>
+        <v>8.766249999999999</v>
       </c>
       <c r="O8" t="n">
         <v>0</v>
@@ -9826,6 +9826,133 @@
       </c>
       <c r="AM74" t="n">
         <v>115.1</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>5511</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>115.2Q</t>
+        </is>
+      </c>
+      <c r="C75" t="n">
+        <v>2943</v>
+      </c>
+      <c r="D75" t="n">
+        <v>2328</v>
+      </c>
+      <c r="E75" t="n">
+        <v>615</v>
+      </c>
+      <c r="F75" t="n">
+        <v>20.89</v>
+      </c>
+      <c r="G75" t="n">
+        <v>479</v>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>16.26%</t>
+        </is>
+      </c>
+      <c r="I75" t="n">
+        <v>107</v>
+      </c>
+      <c r="J75" t="n">
+        <v>586</v>
+      </c>
+      <c r="K75" t="n">
+        <v>465</v>
+      </c>
+      <c r="L75" t="n">
+        <v>3.42</v>
+      </c>
+      <c r="M75" t="n">
+        <v>2.665</v>
+      </c>
+      <c r="N75" t="n">
+        <v>17.61375</v>
+      </c>
+      <c r="O75" t="n">
+        <v>1</v>
+      </c>
+      <c r="P75" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q75" t="n">
+        <v>0</v>
+      </c>
+      <c r="R75" t="n">
+        <v>1</v>
+      </c>
+      <c r="S75" t="n">
+        <v>1</v>
+      </c>
+      <c r="T75" t="n">
+        <v>0</v>
+      </c>
+      <c r="U75" t="n">
+        <v>1</v>
+      </c>
+      <c r="V75" t="n">
+        <v>115.2</v>
+      </c>
+      <c r="W75" t="n">
+        <v>0.8799999999999999</v>
+      </c>
+      <c r="X75" t="n">
+        <v>0.3464566929133859</v>
+      </c>
+      <c r="Y75" t="n">
+        <v>2.16</v>
+      </c>
+      <c r="Z75" t="n">
+        <v>0.1153230112119594</v>
+      </c>
+      <c r="AA75" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="AB75" t="n">
+        <v>0.8486486486486484</v>
+      </c>
+      <c r="AC75" t="n">
+        <v>4.09</v>
+      </c>
+      <c r="AD75" t="n">
+        <v>0.243452380952381</v>
+      </c>
+      <c r="AE75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AH75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AI75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AJ75" t="inlineStr">
+        <is>
+          <t>EPS成長 / 毛利率成長</t>
+        </is>
+      </c>
+      <c r="AK75" t="n">
+        <v>115</v>
+      </c>
+      <c r="AL75" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM75" t="n">
+        <v>115.2</v>
       </c>
     </row>
   </sheetData>
